--- a/AutoBericht/project-template/templates/Vorlage Aktionsplan d.V01.xlsx
+++ b/AutoBericht/project-template/templates/Vorlage Aktionsplan d.V01.xlsx
@@ -1142,7 +1142,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
